--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.971665610957</v>
+        <v>6.820395661780513</v>
       </c>
       <c r="D2" t="n">
-        <v>41.46452968358658</v>
+        <v>6.73798607358282</v>
       </c>
       <c r="E2" t="n">
-        <v>12.47739232271918</v>
+        <v>2.027576252441868</v>
       </c>
       <c r="F2" t="n">
-        <v>12.0104100020306</v>
+        <v>1.951691625329973</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.29617105181858</v>
+        <v>2.64812779592052</v>
       </c>
       <c r="D3" t="n">
-        <v>15.9909371019761</v>
+        <v>2.598527279071117</v>
       </c>
       <c r="E3" t="n">
-        <v>12.47739232271918</v>
+        <v>2.027576252441868</v>
       </c>
       <c r="F3" t="n">
-        <v>12.0104100020306</v>
+        <v>1.951691625329973</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.52159454425631</v>
+        <v>4.634759113441651</v>
       </c>
       <c r="D4" t="n">
-        <v>24.29081564044358</v>
+        <v>3.947257541572082</v>
       </c>
       <c r="E4" t="n">
-        <v>12.47739232271918</v>
+        <v>2.027576252441868</v>
       </c>
       <c r="F4" t="n">
-        <v>12.0104100020306</v>
+        <v>1.951691625329973</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.31912281344749</v>
+        <v>6.876857457185218</v>
       </c>
       <c r="D5" t="n">
-        <v>20.90995414192957</v>
+        <v>3.397867548063556</v>
       </c>
       <c r="E5" t="n">
-        <v>12.47739232271918</v>
+        <v>2.027576252441868</v>
       </c>
       <c r="F5" t="n">
-        <v>12.0104100020306</v>
+        <v>1.951691625329973</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.27350771466423</v>
+        <v>6.706945003632937</v>
       </c>
       <c r="D6" t="n">
-        <v>40.79336231465192</v>
+        <v>6.628921376130936</v>
       </c>
       <c r="E6" t="n">
-        <v>12.47739232271918</v>
+        <v>2.027576252441868</v>
       </c>
       <c r="F6" t="n">
-        <v>12.0104100020306</v>
+        <v>1.951691625329973</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.12033420525601</v>
+        <v>5.219554308354103</v>
       </c>
       <c r="D7" t="n">
-        <v>18.04544731877271</v>
+        <v>2.932385189300565</v>
       </c>
       <c r="E7" t="n">
-        <v>12.47739232271918</v>
+        <v>2.027576252441868</v>
       </c>
       <c r="F7" t="n">
-        <v>12.0104100020306</v>
+        <v>1.951691625329973</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.246211251235321</v>
+        <v>1.34000932832574</v>
       </c>
       <c r="D8" t="n">
-        <v>6.294226239230465</v>
+        <v>1.022811763874951</v>
       </c>
       <c r="E8" t="n">
-        <v>12.47739232271918</v>
+        <v>2.027576252441868</v>
       </c>
       <c r="F8" t="n">
-        <v>12.0104100020306</v>
+        <v>1.951691625329973</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
